--- a/srcproduct/武汉理工大学—学科垂类大模型与创新应用开发—智研——面向人工智能学科科研全流程赋能的垂类大模型应用系统/07—其他材料/智能科研Agent用户使用反馈调查问卷统计表.xlsx
+++ b/srcproduct/武汉理工大学—学科垂类大模型与创新应用开发—智研——面向人工智能学科科研全流程赋能的垂类大模型应用系统/07—其他材料/智能科研Agent用户使用反馈调查问卷统计表.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:ns4="http://schemas.microsoft.com/office/excel/2006/main" xmlns:ns5="http://schemas.microsoft.com/office/excel/2008/2/main">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/drw/Downloads/比赛/AIC-zhi_yan/srcproduct/武汉理工大学—学科垂类大模型与创新应用开发—智研——面向人工智能学科科研全流程赋能的垂类大模型应用系统/07—其他材料/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BDFFF3-721E-DD4F-9650-F322515AD80C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="智能科研Agent用户使用反馈调查问卷（收集结果）" sheetId="1" r:id="rId3"/>
+    <sheet name="智能科研Agent用户使用反馈调查问卷（收集结果）" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -47,9 +55,6 @@
     <t>提交者（自动）</t>
   </si>
   <si>
-    <t>计算机技术-研251</t>
-  </si>
-  <si>
     <t>显著降低</t>
   </si>
   <si>
@@ -72,9 +77,6 @@
   </si>
   <si>
     <t>予在</t>
-  </si>
-  <si>
-    <t>人工智能-2401-赵宇翔</t>
   </si>
   <si>
     <t>有所降低</t>
@@ -118,9 +120,6 @@
   </si>
   <si>
     <t>Lucky</t>
-  </si>
-  <si>
-    <t>计算机2403陈思威</t>
   </si>
   <si>
     <t>全流程一体化（前沿追踪+写作+数据分析打通）, 自动化程度更高，无需人工反复微调</t>
@@ -187,9 +186,6 @@
     <t>0×0</t>
   </si>
   <si>
-    <t>人工智能 2402 谭皓天</t>
-  </si>
-  <si>
     <t>界面简洁、解决了科研读文献的痛点</t>
   </si>
   <si>
@@ -200,21 +196,44 @@
   </si>
   <si>
     <t>tht</t>
+  </si>
+  <si>
+    <t>人工智能 2402 xxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机2403xxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>人工智能-2401-xxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>计算机技术-研xxx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot; hh:mm"/>
+    <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;\ hh:mm"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color indexed="8"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -223,7 +242,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -236,19 +255,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true">
-      <alignment wrapText="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:wp14="http://schemas.microsoft.com/office/word/2010/wordprocessingDrawing" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:wne="http://schemas.microsoft.com/office/word/2006/wordml" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:xvml="urn:schemas-microsoft-com:office:excel" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:pvml="urn:schemas-microsoft-com:office:powerpoint" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:odx="http://opendope.org/xpaths" xmlns:odc="http://opendope.org/conditions" xmlns:odq="http://opendope.org/questions" xmlns:oda="http://opendope.org/answers" xmlns:odi="http://opendope.org/components" xmlns:odgm="http://opendope.org/SmartArt/DataHierarchy" xmlns:b="http://schemas.openxmlformats.org/officeDocument/2006/bibliography" xmlns:w16se="http://schemas.microsoft.com/office/word/2015/wordml/symex" xmlns:w16cid="http://schemas.microsoft.com/office/word/2016/wordml/cid" xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11" xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" name="">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -399,7 +433,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -423,9 +457,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -449,7 +483,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -484,7 +518,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -502,7 +536,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="true">
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -527,7 +561,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -536,30 +570,21 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:ns4="http://schemas.microsoft.com/office/excel/2006/main" xmlns:ns5="http://schemas.microsoft.com/office/excel/2008/2/main">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:K10"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="11" max="11" width="20.0" hidden="false" customWidth="true"/>
-    <col min="5" max="5" width="20.0" hidden="false" customWidth="true"/>
-    <col min="3" max="3" width="20.0" hidden="false" customWidth="true"/>
-    <col min="4" max="4" width="20.0" hidden="false" customWidth="true"/>
-    <col min="10" max="10" width="20.0" hidden="false" customWidth="true"/>
-    <col min="6" max="6" width="20.0" hidden="false" customWidth="true"/>
-    <col min="8" max="8" width="20.0" hidden="false" customWidth="true"/>
-    <col min="9" max="9" width="20.0" hidden="false" customWidth="true"/>
-    <col min="2" max="2" width="20.0" hidden="false" customWidth="true"/>
-    <col min="7" max="7" width="20.0" hidden="false" customWidth="true"/>
-    <col min="1" max="1" width="20.0" hidden="false" customWidth="true"/>
+    <col min="1" max="11" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:11" ht="15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -594,322 +619,323 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" ht="25.75" customHeight="true">
-      <c r="A2" s="1" t="n">
+    <row r="2" spans="1:11" ht="25.75" customHeight="1">
+      <c r="A2" s="1">
         <v>46273.458078703705</v>
       </c>
       <c r="B2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>16</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
         <v>18</v>
       </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
+    </row>
+    <row r="3" spans="1:11" ht="25.75" customHeight="1">
+      <c r="A3" s="1">
+        <v>46276.64806712963</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
         <v>19</v>
       </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="3" ht="25.75" customHeight="true">
-      <c r="A3" s="1" t="n">
-        <v>46276.64806712963</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="4" spans="1:11" ht="25.75" customHeight="1">
+      <c r="A4" s="1">
+        <v>46276.652314814812</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>17</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="25.75" customHeight="1">
+      <c r="A5" s="1">
+        <v>46276.661238425928</v>
+      </c>
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="25.75" customHeight="1">
+      <c r="A6" s="1">
+        <v>46276.675509259258</v>
+      </c>
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" t="s">
+        <v>36</v>
+      </c>
+      <c r="K6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="25.75" customHeight="1">
+      <c r="A7" s="1">
+        <v>46276.675925925927</v>
+      </c>
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>39</v>
+      </c>
+      <c r="I7" t="s">
+        <v>40</v>
+      </c>
+      <c r="J7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="25.75" customHeight="1">
+      <c r="A8" s="1">
+        <v>46276.685497685183</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E8" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
+        <v>44</v>
+      </c>
+      <c r="I8" t="s">
+        <v>45</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="25.75" customHeight="1">
+      <c r="A9" s="1">
+        <v>46277.440254629626</v>
+      </c>
+      <c r="B9" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" t="s">
+        <v>47</v>
+      </c>
+      <c r="E9" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" t="s">
         <v>22</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G9" t="s">
         <v>23</v>
       </c>
-      <c r="F3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" t="s">
-        <v>28</v>
+      <c r="H9" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K9" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="4" ht="25.75" customHeight="true">
-      <c r="A4" s="1" t="n">
-        <v>46276.65231481481</v>
-      </c>
-      <c r="B4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" t="s">
+    <row r="10" spans="1:11" ht="25.75" customHeight="1">
+      <c r="A10" s="1">
+        <v>46277.496921296297</v>
+      </c>
+      <c r="B10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" t="s">
-        <v>18</v>
-      </c>
-      <c r="I4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" ht="25.75" customHeight="true">
-      <c r="A5" s="1" t="n">
-        <v>46276.66123842593</v>
-      </c>
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J5" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" ht="25.75" customHeight="true">
-      <c r="A6" s="1" t="n">
-        <v>46276.67550925926</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>37</v>
-      </c>
-      <c r="I6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J6" t="s">
-        <v>39</v>
-      </c>
-      <c r="K6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" ht="25.75" customHeight="true">
-      <c r="A7" s="1" t="n">
-        <v>46276.67592592593</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I7" t="s">
-        <v>43</v>
-      </c>
-      <c r="J7" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="8" ht="25.75" customHeight="true">
-      <c r="A8" s="1" t="n">
-        <v>46276.68549768518</v>
-      </c>
-      <c r="B8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" t="s">
-        <v>15</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8" t="s">
-        <v>47</v>
-      </c>
-      <c r="I8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" ht="25.75" customHeight="true">
-      <c r="A9" s="1" t="n">
-        <v>46277.440254629626</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" t="s">
-        <v>23</v>
-      </c>
-      <c r="F9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="H10" t="s">
         <v>52</v>
       </c>
-      <c r="J9" t="s">
+      <c r="I10" t="s">
         <v>53</v>
       </c>
-      <c r="K9" t="s">
+      <c r="J10" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="10" ht="25.75" customHeight="true">
-      <c r="A10" s="1" t="n">
-        <v>46277.4969212963</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="K10" t="s">
         <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" t="s">
-        <v>56</v>
-      </c>
-      <c r="I10" t="s">
-        <v>57</v>
-      </c>
-      <c r="J10" t="s">
-        <v>58</v>
-      </c>
-      <c r="K10" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>